--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,31 @@
           <t>min_separation</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>trap_ratio_min</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>trap_ratio_max</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>shake_free_seconds</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>shake_ramp_seconds</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>shake_max_degrees</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +534,31 @@
           <t>float</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -561,6 +611,31 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>min_separation</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>trap_ratio_min</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>trap_ratio_max</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>shake_free_seconds</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>shake_ramp_seconds</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>shake_max_degrees</t>
         </is>
       </c>
     </row>
@@ -588,6 +663,21 @@
       </c>
       <c r="I5" t="n">
         <v>1.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -653,13 +653,13 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
         <v>1.2</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -677,7 +677,7 @@
         <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>750</v>
+        <v>88</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,26 @@
           <t>shake_max_degrees</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>rise_height_min</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>rise_height_max</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>stagger_ticks</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>rest_ticks</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -559,6 +579,26 @@
           <t>float</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -636,6 +676,26 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>shake_max_degrees</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>rise_height_min</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rise_height_max</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>stagger_ticks</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>rest_ticks</t>
         </is>
       </c>
     </row>
@@ -644,22 +704,22 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="n">
         <v>1.2</v>
@@ -678,6 +738,18 @@
       </c>
       <c r="N5" t="n">
         <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -701,7 +701,7 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
         <v>120</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,26 @@
           <t>rest_ticks</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>course_kind</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>range_target_id</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>step_gap_ticks</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>match_duration_ticks</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -599,6 +619,26 @@
           <t>int</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -606,6 +646,10 @@
           <t>##group</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -696,6 +740,26 @@
       <c r="R4" t="inlineStr">
         <is>
           <t>rest_ticks</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>course_kind</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>range_target_id</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>step_gap_ticks</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>match_duration_ticks</t>
         </is>
       </c>
     </row>
@@ -750,6 +814,83 @@
       </c>
       <c r="R5" t="n">
         <v>20</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>120</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+      <c r="R6" t="n">
+        <v>20</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>50</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -646,10 +646,6 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -795,13 +791,13 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.2</v>
@@ -860,13 +856,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -764,7 +764,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -791,13 +791,13 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.2</v>
@@ -856,13 +856,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,11 @@
           <t>match_duration_ticks</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>shake_base_ratio</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -639,6 +644,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -756,6 +766,11 @@
       <c r="V4" t="inlineStr">
         <is>
           <t>match_duration_ticks</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>shake_base_ratio</t>
         </is>
       </c>
     </row>
@@ -823,6 +838,9 @@
       <c r="V5" t="n">
         <v>3000</v>
       </c>
+      <c r="W5" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -887,6 +905,9 @@
       </c>
       <c r="V6" t="n">
         <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -812,7 +812,7 @@
         <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>1.2</v>
@@ -880,7 +880,7 @@
         <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -880,7 +880,7 @@
         <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -880,7 +880,7 @@
         <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -880,7 +880,7 @@
         <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -880,7 +880,7 @@
         <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -416,7 +416,7 @@
   <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:24">
       <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
@@ -532,8 +532,13 @@
           <t>shake_base_ratio</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>arrows_per_stand</t>
+        </is>
+      </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:24">
       <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
@@ -647,6 +652,11 @@
       <c r="W2" t="inlineStr">
         <is>
           <t>float</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -657,7 +667,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:24">
       <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
@@ -773,8 +783,13 @@
           <t>shake_base_ratio</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>arrows_per_stand</t>
+        </is>
+      </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:24">
       <c r="B5" t="n">
         <v>5</v>
       </c>
@@ -841,8 +856,11 @@
       <c r="W5" t="n">
         <v>0.4</v>
       </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:24">
       <c r="B6" t="n">
         <v>6</v>
       </c>
@@ -908,6 +926,9 @@
       </c>
       <c r="W6" t="n">
         <v>0.4</v>
+      </c>
+      <c r="X6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -897,8 +897,8 @@
       <c r="M6" t="n">
         <v>2.5</v>
       </c>
-      <c r="N6" t="n">
-        <v>0.06</v>
+      <c r="N6">
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -416,7 +416,7 @@
   <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:27">
       <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
@@ -537,8 +537,23 @@
           <t>arrows_per_stand</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>box_half_width_m</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>box_half_depth_m</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>move_speed_mps</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:27">
       <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
@@ -657,6 +672,21 @@
       <c r="X2" t="inlineStr">
         <is>
           <t>int</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>float</t>
         </is>
       </c>
     </row>
@@ -667,7 +697,7 @@
         </is>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:27">
       <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
@@ -788,8 +818,23 @@
           <t>arrows_per_stand</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>box_half_width_m</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>box_half_depth_m</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>move_speed_mps</t>
+        </is>
+      </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:27">
       <c r="B5" t="n">
         <v>5</v>
       </c>
@@ -859,8 +904,17 @@
       <c r="X5">
         <v>0</v>
       </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:27">
       <c r="B6" t="n">
         <v>6</v>
       </c>
@@ -929,6 +983,15 @@
       </c>
       <c r="X6">
         <v>3</v>
+      </c>
+      <c r="Y6">
+        <v>2</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -985,13 +985,13 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z6">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AA6">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -413,10 +413,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
@@ -553,7 +553,7 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
@@ -697,7 +697,7 @@
         </is>
       </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
@@ -834,7 +834,7 @@
         </is>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5">
       <c r="B5" t="n">
         <v>5</v>
       </c>
@@ -901,20 +901,20 @@
       <c r="W5" t="n">
         <v>0.4</v>
       </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6">
       <c r="B6" t="n">
         <v>6</v>
       </c>
@@ -951,7 +951,7 @@
       <c r="M6" t="n">
         <v>2.5</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
@@ -981,17 +981,97 @@
       <c r="W6" t="n">
         <v>0.4</v>
       </c>
-      <c r="X6">
+      <c r="X6" t="n">
         <v>3</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" t="n">
         <v>3</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>120</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12</v>
+      </c>
+      <c r="R7" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>200</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,6 +552,16 @@
           <t>move_speed_mps</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>arrow_min_speed_mps</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>arrow_max_speed_mps</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -689,6 +699,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -831,6 +851,16 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>move_speed_mps</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>arrow_min_speed_mps</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>arrow_max_speed_mps</t>
         </is>
       </c>
     </row>
@@ -913,6 +943,12 @@
       <c r="AA5" t="n">
         <v>0</v>
       </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -993,6 +1029,12 @@
       <c r="AA6" t="n">
         <v>4</v>
       </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -1072,6 +1114,12 @@
       </c>
       <c r="AA7" t="n">
         <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -1116,10 +1116,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AC7" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,10 +866,10 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -917,22 +917,22 @@
         <v>20</v>
       </c>
       <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>200</v>
+      </c>
+      <c r="V5" t="n">
         <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>3000</v>
       </c>
       <c r="W5" t="n">
         <v>0.4</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -944,181 +944,9 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>120</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>12</v>
-      </c>
-      <c r="R6" t="n">
-        <v>20</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>50</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>120</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>12</v>
-      </c>
-      <c r="R7" t="n">
-        <v>20</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>200</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AC7" t="n">
         <v>100</v>
       </c>
     </row>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,51 @@
           <t>arrow_max_speed_mps</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>round_count</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>round_intro_ticks</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>round_hunt_ticks</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>round_result_ticks</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>volley_period_ticks</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>volley_cue_ticks</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>volley_quiet_ticks</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>target_life_ticks</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>trap_chance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -709,6 +754,51 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -861,6 +951,51 @@
       <c r="AC4" t="inlineStr">
         <is>
           <t>arrow_max_speed_mps</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>round_count</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>round_intro_ticks</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>round_hunt_ticks</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>round_result_ticks</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>volley_period_ticks</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>volley_cue_ticks</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>volley_quiet_ticks</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>target_life_ticks</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>trap_chance</t>
         </is>
       </c>
     </row>
@@ -948,6 +1083,146 @@
       </c>
       <c r="AC5" t="n">
         <v>100</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1250</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,11 @@
           <t>trap_chance</t>
         </is>
       </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>jackpot_chance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -799,6 +804,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -996,6 +1006,11 @@
       <c r="AL4" t="inlineStr">
         <is>
           <t>trap_chance</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>jackpot_chance</t>
         </is>
       </c>
     </row>
@@ -1111,6 +1126,9 @@
       <c r="AL5" t="n">
         <v>0</v>
       </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -1223,6 +1241,9 @@
       </c>
       <c r="AL6" t="n">
         <v>0.35</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -1210,10 +1210,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AC6" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="AD6" t="n">
         <v>3</v>
@@ -1228,16 +1228,16 @@
         <v>110</v>
       </c>
       <c r="AH6" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AI6" t="n">
         <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="AK6" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AL6" t="n">
         <v>0.35</v>

--- a/table/Datas/#ArcheryConfig.xlsx
+++ b/table/Datas/#ArcheryConfig.xlsx
@@ -1240,7 +1240,7 @@
         <v>180</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="AM6" t="n">
         <v>0.28</v>
